--- a/output/StructureDefinition-BRImunobiologicoAdministrado-3.0.xlsx
+++ b/output/StructureDefinition-BRImunobiologicoAdministrado-3.0.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7074" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7074" uniqueCount="732">
   <si>
     <t>Property</t>
   </si>
@@ -1593,6 +1593,10 @@
   </si>
   <si>
     <t>The quantity of vaccine product that was administered.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>RXA-6 / RXA-7</t>
@@ -16177,16 +16181,16 @@
         <v>82</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>102</v>
+        <v>511</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
@@ -16197,10 +16201,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16223,13 +16227,13 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16280,7 +16284,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16295,13 +16299,13 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
@@ -16312,10 +16316,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16427,10 +16431,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16544,14 +16548,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16573,10 +16577,10 @@
         <v>137</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>164</v>
@@ -16631,7 +16635,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16663,10 +16667,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16692,10 +16696,10 @@
         <v>187</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16726,7 +16730,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -16744,7 +16748,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16759,13 +16763,13 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
@@ -16776,10 +16780,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16891,10 +16895,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17008,10 +17012,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17127,10 +17131,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17242,10 +17246,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17359,10 +17363,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17478,10 +17482,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17595,10 +17599,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17712,10 +17716,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17829,10 +17833,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17948,10 +17952,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18067,10 +18071,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18093,16 +18097,16 @@
         <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18152,7 +18156,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>91</v>
@@ -18167,16 +18171,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18184,10 +18188,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18299,10 +18303,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18416,10 +18420,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18533,10 +18537,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18650,10 +18654,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18767,10 +18771,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18884,10 +18888,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18910,13 +18914,13 @@
         <v>81</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -18967,7 +18971,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18982,13 +18986,13 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
@@ -18999,10 +19003,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19028,10 +19032,10 @@
         <v>187</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19061,10 +19065,10 @@
         <v>191</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19082,7 +19086,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19097,13 +19101,13 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>82</v>
@@ -19114,10 +19118,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19140,13 +19144,13 @@
         <v>82</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19197,7 +19201,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19212,7 +19216,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>82</v>
@@ -19229,10 +19233,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19258,20 +19262,20 @@
         <v>257</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q143" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="R143" t="s" s="2">
         <v>82</v>
@@ -19316,7 +19320,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19334,7 +19338,7 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>133</v>
@@ -19348,10 +19352,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19377,10 +19381,10 @@
         <v>187</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19410,10 +19414,10 @@
         <v>191</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>82</v>
@@ -19431,7 +19435,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19463,10 +19467,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19489,13 +19493,13 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19546,7 +19550,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19558,7 +19562,7 @@
         <v>82</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>82</v>
@@ -19578,10 +19582,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19693,10 +19697,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19810,14 +19814,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -19839,10 +19843,10 @@
         <v>137</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>164</v>
@@ -19897,7 +19901,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19929,10 +19933,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19958,10 +19962,10 @@
         <v>206</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20012,7 +20016,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20030,7 +20034,7 @@
         <v>82</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>133</v>
@@ -20044,10 +20048,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20073,10 +20077,10 @@
         <v>104</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20127,7 +20131,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20159,10 +20163,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20188,10 +20192,10 @@
         <v>369</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20242,7 +20246,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20260,7 +20264,7 @@
         <v>82</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>133</v>
@@ -20274,10 +20278,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20303,10 +20307,10 @@
         <v>369</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20357,7 +20361,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -20375,7 +20379,7 @@
         <v>82</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>133</v>
@@ -20389,10 +20393,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20418,10 +20422,10 @@
         <v>187</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -20451,10 +20455,10 @@
         <v>191</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -20472,7 +20476,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20490,7 +20494,7 @@
         <v>82</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>133</v>
@@ -20504,10 +20508,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20533,10 +20537,10 @@
         <v>187</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -20566,10 +20570,10 @@
         <v>191</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>82</v>
@@ -20587,7 +20591,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20619,10 +20623,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20645,16 +20649,16 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -20704,7 +20708,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20722,10 +20726,10 @@
         <v>82</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>82</v>
@@ -20736,10 +20740,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20851,10 +20855,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20968,14 +20972,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -20997,10 +21001,10 @@
         <v>137</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>164</v>
@@ -21055,7 +21059,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21087,10 +21091,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21116,10 +21120,10 @@
         <v>369</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -21170,7 +21174,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21188,7 +21192,7 @@
         <v>82</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>375</v>
@@ -21202,10 +21206,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21228,13 +21232,13 @@
         <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21285,7 +21289,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21303,10 +21307,10 @@
         <v>82</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>82</v>
@@ -21317,10 +21321,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21346,10 +21350,10 @@
         <v>257</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21400,7 +21404,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21418,10 +21422,10 @@
         <v>82</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>82</v>
@@ -21432,10 +21436,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21458,13 +21462,13 @@
         <v>82</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -21515,7 +21519,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21547,10 +21551,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21662,10 +21666,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21775,13 +21779,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="B165" t="s" s="2">
-        <v>649</v>
-      </c>
       <c r="C165" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>82</v>
@@ -21803,13 +21807,13 @@
         <v>82</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -21892,16 +21896,16 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -21920,13 +21924,13 @@
         <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22009,10 +22013,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22124,10 +22128,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22239,19 +22243,19 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B169" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="B169" t="s" s="2">
-        <v>664</v>
-      </c>
       <c r="C169" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E169" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F169" t="s" s="2">
         <v>79</v>
@@ -22272,10 +22276,10 @@
         <v>137</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22358,10 +22362,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22473,10 +22477,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22590,10 +22594,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22619,13 +22623,13 @@
         <v>104</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -22633,7 +22637,7 @@
       </c>
       <c r="Q172" s="2"/>
       <c r="R172" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="S172" t="s" s="2">
         <v>82</v>
@@ -22675,7 +22679,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>91</v>
@@ -22707,10 +22711,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22736,10 +22740,10 @@
         <v>206</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -22790,7 +22794,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -22822,19 +22826,19 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F174" t="s" s="2">
         <v>79</v>
@@ -22855,10 +22859,10 @@
         <v>137</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -22941,10 +22945,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23056,10 +23060,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23173,10 +23177,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23202,13 +23206,13 @@
         <v>104</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23216,7 +23220,7 @@
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>82</v>
@@ -23258,7 +23262,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>91</v>
@@ -23290,10 +23294,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23319,10 +23323,10 @@
         <v>206</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -23373,7 +23377,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23405,19 +23409,19 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E179" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F179" t="s" s="2">
         <v>79</v>
@@ -23438,10 +23442,10 @@
         <v>137</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23524,10 +23528,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23639,10 +23643,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23756,10 +23760,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23785,13 +23789,13 @@
         <v>104</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -23799,7 +23803,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>82</v>
@@ -23841,7 +23845,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>91</v>
@@ -23873,10 +23877,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23902,10 +23906,10 @@
         <v>206</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -23956,7 +23960,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -23988,10 +23992,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24017,13 +24021,13 @@
         <v>104</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24031,7 +24035,7 @@
       </c>
       <c r="Q184" s="2"/>
       <c r="R184" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="S184" t="s" s="2">
         <v>82</v>
@@ -24073,7 +24077,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>91</v>
@@ -24105,10 +24109,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24131,13 +24135,13 @@
         <v>82</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -24188,7 +24192,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -24220,14 +24224,14 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
@@ -24249,10 +24253,10 @@
         <v>137</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N186" t="s" s="2">
         <v>164</v>
@@ -24307,7 +24311,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24339,10 +24343,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24368,10 +24372,10 @@
         <v>206</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -24422,7 +24426,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24454,10 +24458,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24483,10 +24487,10 @@
         <v>348</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -24537,7 +24541,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24569,10 +24573,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24598,10 +24602,10 @@
         <v>187</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -24631,10 +24635,10 @@
         <v>191</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>82</v>
@@ -24652,7 +24656,7 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -24684,10 +24688,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24713,13 +24717,13 @@
         <v>206</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -24748,10 +24752,10 @@
         <v>180</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>82</v>
@@ -24769,7 +24773,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>91</v>
@@ -24801,10 +24805,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24827,16 +24831,16 @@
         <v>82</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -24886,7 +24890,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
